--- a/research/traditional_assets/database/data/iceland/iceland_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_bank_money_center.xlsx
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0348</v>
+        <v>0.0299</v>
       </c>
       <c r="E2">
-        <v>0.002250000000000002</v>
+        <v>0.1235</v>
+      </c>
+      <c r="F2">
+        <v>0.0794</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>368.8</v>
+        <v>364</v>
       </c>
       <c r="L2">
-        <v>0.4406739156410562</v>
+        <v>0.4597120484970952</v>
       </c>
       <c r="M2">
-        <v>222.3</v>
+        <v>324.3</v>
       </c>
       <c r="N2">
-        <v>0.05345034864150035</v>
+        <v>0.1004553480159836</v>
       </c>
       <c r="O2">
-        <v>0.6027657266811279</v>
+        <v>0.890934065934066</v>
       </c>
       <c r="P2">
-        <v>48.1</v>
+        <v>238.2</v>
       </c>
       <c r="Q2">
-        <v>0.01156528011541236</v>
+        <v>0.07378496422265589</v>
       </c>
       <c r="R2">
-        <v>0.1304229934924078</v>
+        <v>0.6543956043956044</v>
       </c>
       <c r="S2">
-        <v>174.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="T2">
-        <v>0.783625730994152</v>
+        <v>0.2654949121184089</v>
       </c>
       <c r="U2">
-        <v>1706</v>
+        <v>1705.4</v>
       </c>
       <c r="V2">
-        <v>0.4101947583553739</v>
+        <v>0.528265650652046</v>
       </c>
       <c r="W2">
-        <v>0.1363546026816755</v>
+        <v>0.1211107569806036</v>
       </c>
       <c r="X2">
-        <v>0.08168383029767515</v>
+        <v>0.1245804314791603</v>
       </c>
       <c r="Y2">
-        <v>0.05467077238400031</v>
+        <v>-0.003469674498556632</v>
       </c>
       <c r="Z2">
-        <v>0.1334902869028308</v>
+        <v>0.09691839172754156</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04978179161046839</v>
+        <v>0.07817989155525827</v>
       </c>
       <c r="AC2">
-        <v>-0.04978179161046839</v>
+        <v>-0.07817989155525827</v>
       </c>
       <c r="AD2">
-        <v>6874.5</v>
+        <v>6561.799999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6874.5</v>
+        <v>6561.799999999999</v>
       </c>
       <c r="AG2">
-        <v>5168.5</v>
+        <v>4856.4</v>
       </c>
       <c r="AH2">
-        <v>0.623057053518829</v>
+        <v>0.670248516358362</v>
       </c>
       <c r="AI2">
-        <v>0.6953702673450602</v>
+        <v>0.7042220266586533</v>
       </c>
       <c r="AJ2">
-        <v>0.5541141785044225</v>
+        <v>0.6006901925859958</v>
       </c>
       <c r="AK2">
-        <v>0.6318382415862887</v>
+        <v>0.6379591193316169</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0568</v>
+        <v>0.0196</v>
       </c>
       <c r="E3">
-        <v>-0.0355</v>
+        <v>0.128</v>
+      </c>
+      <c r="F3">
+        <v>0.0794</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>213.9</v>
+        <v>186.4</v>
       </c>
       <c r="L3">
-        <v>0.4698001317812431</v>
+        <v>0.470825966153069</v>
       </c>
       <c r="M3">
-        <v>196.2</v>
+        <v>241.9</v>
       </c>
       <c r="N3">
-        <v>0.0883465417867435</v>
+        <v>0.1569250729808628</v>
       </c>
       <c r="O3">
-        <v>0.9172510518934081</v>
+        <v>1.29774678111588</v>
       </c>
       <c r="P3">
-        <v>22</v>
+        <v>155.8</v>
       </c>
       <c r="Q3">
-        <v>0.009906340057636886</v>
+        <v>0.1010703859876743</v>
       </c>
       <c r="R3">
-        <v>0.1028517999064984</v>
+        <v>0.8358369098712447</v>
       </c>
       <c r="S3">
-        <v>174.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="T3">
-        <v>0.8878695208970439</v>
+        <v>0.3559322033898305</v>
       </c>
       <c r="U3">
-        <v>662.2</v>
+        <v>773.3</v>
       </c>
       <c r="V3">
-        <v>0.2981808357348703</v>
+        <v>0.5016542328900422</v>
       </c>
       <c r="W3">
-        <v>0.1539845943416601</v>
+        <v>0.1251174654316016</v>
       </c>
       <c r="X3">
-        <v>0.07910531728151218</v>
+        <v>0.1230213010302098</v>
       </c>
       <c r="Y3">
-        <v>0.07487927706014791</v>
+        <v>0.002096164401391765</v>
       </c>
       <c r="Z3">
-        <v>0.1445318824063463</v>
+        <v>0.09293514493093831</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04962607312524585</v>
+        <v>0.07811502624267466</v>
       </c>
       <c r="AC3">
-        <v>-0.04962607312524585</v>
+        <v>-0.07811502624267466</v>
       </c>
       <c r="AD3">
-        <v>3437.5</v>
+        <v>3037.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3437.5</v>
+        <v>3037.2</v>
       </c>
       <c r="AG3">
-        <v>2775.3</v>
+        <v>2263.9</v>
       </c>
       <c r="AH3">
-        <v>0.6075146245338706</v>
+        <v>0.6633323869220521</v>
       </c>
       <c r="AI3">
-        <v>0.696908261530664</v>
+        <v>0.7018370883882149</v>
       </c>
       <c r="AJ3">
-        <v>0.5554932847621145</v>
+        <v>0.5949177484627108</v>
       </c>
       <c r="AK3">
-        <v>0.6499075006439828</v>
+        <v>0.6369647177986607</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0128</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="E4">
-        <v>0.04</v>
+        <v>0.119</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>154.9</v>
+        <v>177.6</v>
       </c>
       <c r="L4">
-        <v>0.4059224318658281</v>
+        <v>0.4485981308411215</v>
       </c>
       <c r="M4">
-        <v>26.1</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N4">
-        <v>0.01346610256939428</v>
+        <v>0.04884989328906806</v>
       </c>
       <c r="O4">
-        <v>0.1684958037443512</v>
+        <v>0.463963963963964</v>
       </c>
       <c r="P4">
-        <v>26.1</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="Q4">
-        <v>0.01346610256939428</v>
+        <v>0.04884989328906806</v>
       </c>
       <c r="R4">
-        <v>0.1684958037443512</v>
+        <v>0.463963963963964</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +886,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1043.8</v>
+        <v>932.1</v>
       </c>
       <c r="V4">
-        <v>0.5385409142503353</v>
+        <v>0.5525847759070429</v>
       </c>
       <c r="W4">
-        <v>0.1187246110216908</v>
+        <v>0.1171040485296057</v>
       </c>
       <c r="X4">
-        <v>0.08426234331383811</v>
+        <v>0.1261395619281107</v>
       </c>
       <c r="Y4">
-        <v>0.0344622677078527</v>
+        <v>-0.009035513398505043</v>
       </c>
       <c r="Z4">
-        <v>0.1223390612977687</v>
+        <v>0.101258376387539</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04993751009569094</v>
+        <v>0.07824475686784188</v>
       </c>
       <c r="AC4">
-        <v>-0.04993751009569094</v>
+        <v>-0.07824475686784188</v>
       </c>
       <c r="AD4">
-        <v>3437</v>
+        <v>3524.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3437</v>
+        <v>3524.6</v>
       </c>
       <c r="AG4">
-        <v>2393.2</v>
+        <v>2592.5</v>
       </c>
       <c r="AH4">
-        <v>0.6394180681649055</v>
+        <v>0.6763249798518632</v>
       </c>
       <c r="AI4">
-        <v>0.6938388242894057</v>
+        <v>0.706290202993808</v>
       </c>
       <c r="AJ4">
-        <v>0.5525234335318835</v>
+        <v>0.6058233823288856</v>
       </c>
       <c r="AK4">
-        <v>0.6121029208655174</v>
+        <v>0.6388300231629787</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/iceland/iceland_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0299</v>
+        <v>0.07325</v>
       </c>
       <c r="E2">
-        <v>0.1235</v>
+        <v>0.17</v>
       </c>
       <c r="F2">
-        <v>0.0794</v>
+        <v>0.167</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>364</v>
+        <v>351.8</v>
       </c>
       <c r="L2">
-        <v>0.4597120484970952</v>
+        <v>0.3856610392457794</v>
       </c>
       <c r="M2">
-        <v>324.3</v>
+        <v>234.6</v>
       </c>
       <c r="N2">
-        <v>0.1004553480159836</v>
+        <v>0.07267207731862958</v>
       </c>
       <c r="O2">
-        <v>0.890934065934066</v>
+        <v>0.6668561682774303</v>
       </c>
       <c r="P2">
-        <v>238.2</v>
+        <v>179.3</v>
       </c>
       <c r="Q2">
-        <v>0.07378496422265589</v>
+        <v>0.05554178799330897</v>
       </c>
       <c r="R2">
-        <v>0.6543956043956044</v>
+        <v>0.5096645821489483</v>
       </c>
       <c r="S2">
-        <v>86.09999999999999</v>
+        <v>55.3</v>
       </c>
       <c r="T2">
-        <v>0.2654949121184089</v>
+        <v>0.2357203751065644</v>
       </c>
       <c r="U2">
-        <v>1705.4</v>
+        <v>1564.8</v>
       </c>
       <c r="V2">
-        <v>0.528265650652046</v>
+        <v>0.4847283315779692</v>
       </c>
       <c r="W2">
-        <v>0.1211107569806036</v>
+        <v>0.1283554688253611</v>
       </c>
       <c r="X2">
-        <v>0.1245804314791603</v>
+        <v>0.1027563530734176</v>
       </c>
       <c r="Y2">
-        <v>-0.003469674498556632</v>
+        <v>0.02559911575194354</v>
       </c>
       <c r="Z2">
-        <v>0.09691839172754156</v>
+        <v>0.1199794290915261</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07817989155525827</v>
+        <v>0.06647210106862803</v>
       </c>
       <c r="AC2">
-        <v>-0.07817989155525827</v>
+        <v>-0.06647210106862803</v>
       </c>
       <c r="AD2">
-        <v>6561.799999999999</v>
+        <v>7195.799999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6561.799999999999</v>
+        <v>7195.799999999999</v>
       </c>
       <c r="AG2">
-        <v>4856.4</v>
+        <v>5630.999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.670248516358362</v>
+        <v>0.6903108211818879</v>
       </c>
       <c r="AI2">
-        <v>0.7042220266586533</v>
+        <v>0.7055051718221481</v>
       </c>
       <c r="AJ2">
-        <v>0.6006901925859958</v>
+        <v>0.6356104388658118</v>
       </c>
       <c r="AK2">
-        <v>0.6379591193316169</v>
+        <v>0.6521361483317313</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0196</v>
+        <v>0.0848</v>
       </c>
       <c r="E3">
-        <v>0.128</v>
+        <v>0.201</v>
       </c>
       <c r="F3">
-        <v>0.0794</v>
+        <v>0.167</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>186.4</v>
+        <v>174.5</v>
       </c>
       <c r="L3">
-        <v>0.470825966153069</v>
+        <v>0.3870037702373032</v>
       </c>
       <c r="M3">
-        <v>241.9</v>
+        <v>138.5</v>
       </c>
       <c r="N3">
-        <v>0.1569250729808628</v>
+        <v>0.08580633170187721</v>
       </c>
       <c r="O3">
-        <v>1.29774678111588</v>
+        <v>0.7936962750716332</v>
       </c>
       <c r="P3">
-        <v>155.8</v>
+        <v>90</v>
       </c>
       <c r="Q3">
-        <v>0.1010703859876743</v>
+        <v>0.05575862709869277</v>
       </c>
       <c r="R3">
-        <v>0.8358369098712447</v>
+        <v>0.5157593123209169</v>
       </c>
       <c r="S3">
-        <v>86.09999999999999</v>
+        <v>48.5</v>
       </c>
       <c r="T3">
-        <v>0.3559322033898305</v>
+        <v>0.3501805054151624</v>
       </c>
       <c r="U3">
-        <v>773.3</v>
+        <v>841.9</v>
       </c>
       <c r="V3">
-        <v>0.5016542328900422</v>
+        <v>0.5215909794932161</v>
       </c>
       <c r="W3">
-        <v>0.1251174654316016</v>
+        <v>0.1357448463632828</v>
       </c>
       <c r="X3">
-        <v>0.1230213010302098</v>
+        <v>0.1020638895429616</v>
       </c>
       <c r="Y3">
-        <v>0.002096164401391765</v>
+        <v>0.03368095682032116</v>
       </c>
       <c r="Z3">
-        <v>0.09293514493093831</v>
+        <v>0.1272014827478229</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07811502624267466</v>
+        <v>0.06644753627807667</v>
       </c>
       <c r="AC3">
-        <v>-0.07811502624267466</v>
+        <v>-0.06644753627807667</v>
       </c>
       <c r="AD3">
-        <v>3037.2</v>
+        <v>3537.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3037.2</v>
+        <v>3537.1</v>
       </c>
       <c r="AG3">
-        <v>2263.9</v>
+        <v>2695.2</v>
       </c>
       <c r="AH3">
-        <v>0.6633323869220521</v>
+        <v>0.6866555365740021</v>
       </c>
       <c r="AI3">
-        <v>0.7018370883882149</v>
+        <v>0.7159976518693952</v>
       </c>
       <c r="AJ3">
-        <v>0.5949177484627108</v>
+        <v>0.6254380061726963</v>
       </c>
       <c r="AK3">
-        <v>0.6369647177986607</v>
+        <v>0.6576545800595384</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.04019999999999999</v>
+        <v>0.0617</v>
       </c>
       <c r="E4">
-        <v>0.119</v>
+        <v>0.139</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,85 +856,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>177.6</v>
+        <v>177.3</v>
       </c>
       <c r="L4">
-        <v>0.4485981308411215</v>
+        <v>0.3843485800997182</v>
       </c>
       <c r="M4">
-        <v>82.40000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N4">
-        <v>0.04884989328906806</v>
+        <v>0.05953782293538195</v>
       </c>
       <c r="O4">
-        <v>0.463963963963964</v>
+        <v>0.542019176536943</v>
       </c>
       <c r="P4">
-        <v>82.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="Q4">
-        <v>0.04884989328906806</v>
+        <v>0.05532494888792516</v>
       </c>
       <c r="R4">
-        <v>0.463963963963964</v>
+        <v>0.5036661026508742</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>6.799999999999997</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.0707596253902185</v>
       </c>
       <c r="U4">
-        <v>932.1</v>
+        <v>722.9</v>
       </c>
       <c r="V4">
-        <v>0.5525847759070429</v>
+        <v>0.4478656836627223</v>
       </c>
       <c r="W4">
-        <v>0.1171040485296057</v>
+        <v>0.1209660912874395</v>
       </c>
       <c r="X4">
-        <v>0.1261395619281107</v>
+        <v>0.1034488166038735</v>
       </c>
       <c r="Y4">
-        <v>-0.009035513398505043</v>
+        <v>0.01751727468356591</v>
       </c>
       <c r="Z4">
-        <v>0.101258376387539</v>
+        <v>0.113671085703021</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07824475686784188</v>
+        <v>0.06649666585917938</v>
       </c>
       <c r="AC4">
-        <v>-0.07824475686784188</v>
+        <v>-0.06649666585917938</v>
       </c>
       <c r="AD4">
-        <v>3524.6</v>
+        <v>3658.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3524.6</v>
+        <v>3658.7</v>
       </c>
       <c r="AG4">
-        <v>2592.5</v>
+        <v>2935.8</v>
       </c>
       <c r="AH4">
-        <v>0.6763249798518632</v>
+        <v>0.6938818085267791</v>
       </c>
       <c r="AI4">
-        <v>0.706290202993808</v>
+        <v>0.6956496938814314</v>
       </c>
       <c r="AJ4">
-        <v>0.6058233823288856</v>
+        <v>0.6452449504384712</v>
       </c>
       <c r="AK4">
-        <v>0.6388300231629787</v>
+        <v>0.6471508872478783</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/iceland/iceland_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07325</v>
+        <v>0.0862</v>
       </c>
       <c r="E2">
-        <v>0.17</v>
-      </c>
-      <c r="F2">
-        <v>0.167</v>
+        <v>0.23</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>351.8</v>
+        <v>179.3</v>
       </c>
       <c r="L2">
-        <v>0.3856610392457794</v>
+        <v>0.384269181311616</v>
       </c>
       <c r="M2">
-        <v>234.6</v>
+        <v>151.7</v>
       </c>
       <c r="N2">
-        <v>0.07267207731862958</v>
+        <v>0.08866678356420596</v>
       </c>
       <c r="O2">
-        <v>0.6668561682774303</v>
+        <v>0.8460680423870607</v>
       </c>
       <c r="P2">
-        <v>179.3</v>
+        <v>91.2</v>
       </c>
       <c r="Q2">
-        <v>0.05554178799330897</v>
+        <v>0.0533052779238997</v>
       </c>
       <c r="R2">
-        <v>0.5096645821489483</v>
+        <v>0.5086447295036252</v>
       </c>
       <c r="S2">
-        <v>55.3</v>
+        <v>60.49999999999999</v>
       </c>
       <c r="T2">
-        <v>0.2357203751065644</v>
+        <v>0.3988134475939353</v>
       </c>
       <c r="U2">
-        <v>1564.8</v>
+        <v>609.3</v>
       </c>
       <c r="V2">
-        <v>0.4847283315779692</v>
+        <v>0.3561283534981588</v>
       </c>
       <c r="W2">
-        <v>0.1283554688253611</v>
+        <v>0.1120134940963329</v>
       </c>
       <c r="X2">
-        <v>0.1027563530734176</v>
+        <v>0.09682539767903858</v>
       </c>
       <c r="Y2">
-        <v>0.02559911575194354</v>
+        <v>0.01518809641729428</v>
       </c>
       <c r="Z2">
-        <v>0.1199794290915261</v>
+        <v>0.1028546236085088</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06647210106862803</v>
+        <v>0.06704788386596955</v>
       </c>
       <c r="AC2">
-        <v>-0.06647210106862803</v>
+        <v>-0.06704788386596955</v>
       </c>
       <c r="AD2">
-        <v>7195.799999999999</v>
+        <v>3117.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7195.799999999999</v>
+        <v>3117.8</v>
       </c>
       <c r="AG2">
-        <v>5630.999999999999</v>
+        <v>2508.5</v>
       </c>
       <c r="AH2">
-        <v>0.6903108211818879</v>
+        <v>0.6456810321618655</v>
       </c>
       <c r="AI2">
-        <v>0.7055051718221481</v>
+        <v>0.6531475856289934</v>
       </c>
       <c r="AJ2">
-        <v>0.6356104388658118</v>
+        <v>0.5945158079347775</v>
       </c>
       <c r="AK2">
-        <v>0.6521361483317313</v>
+        <v>0.6023966187983286</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arion banki hf. (ICSE:ARION)</t>
+          <t>Íslandsbanki hf. (ICSE:ISB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0848</v>
+        <v>0.0862</v>
       </c>
       <c r="E3">
-        <v>0.201</v>
-      </c>
-      <c r="F3">
-        <v>0.167</v>
+        <v>0.23</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,212 +728,90 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>174.5</v>
+        <v>179.3</v>
       </c>
       <c r="L3">
-        <v>0.3870037702373032</v>
+        <v>0.384269181311616</v>
       </c>
       <c r="M3">
-        <v>138.5</v>
+        <v>151.7</v>
       </c>
       <c r="N3">
-        <v>0.08580633170187721</v>
+        <v>0.08866678356420596</v>
       </c>
       <c r="O3">
-        <v>0.7936962750716332</v>
+        <v>0.8460680423870607</v>
       </c>
       <c r="P3">
-        <v>90</v>
+        <v>91.2</v>
       </c>
       <c r="Q3">
-        <v>0.05575862709869277</v>
+        <v>0.0533052779238997</v>
       </c>
       <c r="R3">
-        <v>0.5157593123209169</v>
+        <v>0.5086447295036252</v>
       </c>
       <c r="S3">
-        <v>48.5</v>
+        <v>60.49999999999999</v>
       </c>
       <c r="T3">
-        <v>0.3501805054151624</v>
+        <v>0.3988134475939353</v>
       </c>
       <c r="U3">
-        <v>841.9</v>
+        <v>609.3</v>
       </c>
       <c r="V3">
-        <v>0.5215909794932161</v>
+        <v>0.3561283534981588</v>
       </c>
       <c r="W3">
-        <v>0.1357448463632828</v>
+        <v>0.1120134940963329</v>
       </c>
       <c r="X3">
-        <v>0.1020638895429616</v>
+        <v>0.09682539767903858</v>
       </c>
       <c r="Y3">
-        <v>0.03368095682032116</v>
+        <v>0.01518809641729428</v>
       </c>
       <c r="Z3">
-        <v>0.1272014827478229</v>
+        <v>0.1028546236085088</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06644753627807667</v>
+        <v>0.06704788386596955</v>
       </c>
       <c r="AC3">
-        <v>-0.06644753627807667</v>
+        <v>-0.06704788386596955</v>
       </c>
       <c r="AD3">
-        <v>3537.1</v>
+        <v>3117.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3537.1</v>
+        <v>3117.8</v>
       </c>
       <c r="AG3">
-        <v>2695.2</v>
+        <v>2508.5</v>
       </c>
       <c r="AH3">
-        <v>0.6866555365740021</v>
+        <v>0.6456810321618655</v>
       </c>
       <c r="AI3">
-        <v>0.7159976518693952</v>
+        <v>0.6531475856289934</v>
       </c>
       <c r="AJ3">
-        <v>0.6254380061726963</v>
+        <v>0.5945158079347775</v>
       </c>
       <c r="AK3">
-        <v>0.6576545800595384</v>
+        <v>0.6023966187983286</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Íslandsbanki hf. (ICSE:ISB)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.0617</v>
-      </c>
-      <c r="E4">
-        <v>0.139</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>177.3</v>
-      </c>
-      <c r="L4">
-        <v>0.3843485800997182</v>
-      </c>
-      <c r="M4">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="N4">
-        <v>0.05953782293538195</v>
-      </c>
-      <c r="O4">
-        <v>0.542019176536943</v>
-      </c>
-      <c r="P4">
-        <v>89.3</v>
-      </c>
-      <c r="Q4">
-        <v>0.05532494888792516</v>
-      </c>
-      <c r="R4">
-        <v>0.5036661026508742</v>
-      </c>
-      <c r="S4">
-        <v>6.799999999999997</v>
-      </c>
-      <c r="T4">
-        <v>0.0707596253902185</v>
-      </c>
-      <c r="U4">
-        <v>722.9</v>
-      </c>
-      <c r="V4">
-        <v>0.4478656836627223</v>
-      </c>
-      <c r="W4">
-        <v>0.1209660912874395</v>
-      </c>
-      <c r="X4">
-        <v>0.1034488166038735</v>
-      </c>
-      <c r="Y4">
-        <v>0.01751727468356591</v>
-      </c>
-      <c r="Z4">
-        <v>0.113671085703021</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.06649666585917938</v>
-      </c>
-      <c r="AC4">
-        <v>-0.06649666585917938</v>
-      </c>
-      <c r="AD4">
-        <v>3658.7</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>3658.7</v>
-      </c>
-      <c r="AG4">
-        <v>2935.8</v>
-      </c>
-      <c r="AH4">
-        <v>0.6938818085267791</v>
-      </c>
-      <c r="AI4">
-        <v>0.6956496938814314</v>
-      </c>
-      <c r="AJ4">
-        <v>0.6452449504384712</v>
-      </c>
-      <c r="AK4">
-        <v>0.6471508872478783</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/iceland/iceland_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0862</v>
+        <v>0.07569999999999999</v>
       </c>
       <c r="E2">
-        <v>0.23</v>
+        <v>0.288</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>179.3</v>
+        <v>357.7</v>
       </c>
       <c r="L2">
-        <v>0.384269181311616</v>
+        <v>0.3872050227321932</v>
       </c>
       <c r="M2">
-        <v>151.7</v>
+        <v>340.8</v>
       </c>
       <c r="N2">
-        <v>0.08866678356420596</v>
+        <v>0.0997045142037974</v>
       </c>
       <c r="O2">
-        <v>0.8460680423870607</v>
+        <v>0.9527537042214144</v>
       </c>
       <c r="P2">
-        <v>91.2</v>
+        <v>188</v>
       </c>
       <c r="Q2">
-        <v>0.0533052779238997</v>
+        <v>0.05500131652087416</v>
       </c>
       <c r="R2">
-        <v>0.5086447295036252</v>
+        <v>0.5255800950517192</v>
       </c>
       <c r="S2">
-        <v>60.49999999999999</v>
+        <v>152.8</v>
       </c>
       <c r="T2">
-        <v>0.3988134475939353</v>
+        <v>0.4483568075117371</v>
       </c>
       <c r="U2">
-        <v>609.3</v>
+        <v>1344.7</v>
       </c>
       <c r="V2">
-        <v>0.3561283534981588</v>
+        <v>0.3934056932213802</v>
       </c>
       <c r="W2">
-        <v>0.1120134940963329</v>
+        <v>0.1198030565890046</v>
       </c>
       <c r="X2">
-        <v>0.09682539767903858</v>
+        <v>0.09933520271466129</v>
       </c>
       <c r="Y2">
-        <v>0.01518809641729428</v>
+        <v>0.02046785387434336</v>
       </c>
       <c r="Z2">
-        <v>0.1028546236085088</v>
+        <v>0.1071124622880187</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06704788386596955</v>
+        <v>0.06580133588358258</v>
       </c>
       <c r="AC2">
-        <v>-0.06704788386596955</v>
+        <v>-0.06580133588358258</v>
       </c>
       <c r="AD2">
-        <v>3117.8</v>
+        <v>6749.700000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3117.8</v>
+        <v>6749.700000000001</v>
       </c>
       <c r="AG2">
-        <v>2508.5</v>
+        <v>5405.000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.6456810321618655</v>
+        <v>0.6638309172092292</v>
       </c>
       <c r="AI2">
-        <v>0.6531475856289934</v>
+        <v>0.683306337315246</v>
       </c>
       <c r="AJ2">
-        <v>0.5945158079347775</v>
+        <v>0.6125964796953451</v>
       </c>
       <c r="AK2">
-        <v>0.6023966187983286</v>
+        <v>0.6334009117223114</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,117 +701,239 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Arion banki hf. (ICSE:ARION)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.346</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>178.4</v>
+      </c>
+      <c r="L3">
+        <v>0.3902012248468942</v>
+      </c>
+      <c r="M3">
+        <v>189.1</v>
+      </c>
+      <c r="N3">
+        <v>0.1107661668228678</v>
+      </c>
+      <c r="O3">
+        <v>1.059977578475336</v>
+      </c>
+      <c r="P3">
+        <v>96.8</v>
+      </c>
+      <c r="Q3">
+        <v>0.05670103092783505</v>
+      </c>
+      <c r="R3">
+        <v>0.5426008968609866</v>
+      </c>
+      <c r="S3">
+        <v>92.3</v>
+      </c>
+      <c r="T3">
+        <v>0.4881015335801163</v>
+      </c>
+      <c r="U3">
+        <v>735.4</v>
+      </c>
+      <c r="V3">
+        <v>0.4307638238050609</v>
+      </c>
+      <c r="W3">
+        <v>0.1275926190816764</v>
+      </c>
+      <c r="X3">
+        <v>0.1018675358606116</v>
+      </c>
+      <c r="Y3">
+        <v>0.02572508322106484</v>
+      </c>
+      <c r="Z3">
+        <v>0.1118373417349954</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.06456277003799424</v>
+      </c>
+      <c r="AC3">
+        <v>-0.06456277003799424</v>
+      </c>
+      <c r="AD3">
+        <v>3631.9</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>3631.9</v>
+      </c>
+      <c r="AG3">
+        <v>2896.5</v>
+      </c>
+      <c r="AH3">
+        <v>0.6802457342997883</v>
+      </c>
+      <c r="AI3">
+        <v>0.7115094524439221</v>
+      </c>
+      <c r="AJ3">
+        <v>0.6291678432565111</v>
+      </c>
+      <c r="AK3">
+        <v>0.6629511798768625</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Íslandsbanki hf. (ICSE:ISB)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>0.0862</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>0.23</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>179.3</v>
       </c>
-      <c r="L3">
+      <c r="L4">
         <v>0.384269181311616</v>
       </c>
-      <c r="M3">
+      <c r="M4">
         <v>151.7</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <v>0.08866678356420596</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <v>0.8460680423870607</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <v>91.2</v>
       </c>
-      <c r="Q3">
+      <c r="Q4">
         <v>0.0533052779238997</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <v>0.5086447295036252</v>
       </c>
-      <c r="S3">
+      <c r="S4">
         <v>60.49999999999999</v>
       </c>
-      <c r="T3">
+      <c r="T4">
         <v>0.3988134475939353</v>
       </c>
-      <c r="U3">
+      <c r="U4">
         <v>609.3</v>
       </c>
-      <c r="V3">
+      <c r="V4">
         <v>0.3561283534981588</v>
       </c>
-      <c r="W3">
+      <c r="W4">
         <v>0.1120134940963329</v>
       </c>
-      <c r="X3">
-        <v>0.09682539767903858</v>
-      </c>
-      <c r="Y3">
-        <v>0.01518809641729428</v>
-      </c>
-      <c r="Z3">
+      <c r="X4">
+        <v>0.09680286956871098</v>
+      </c>
+      <c r="Y4">
+        <v>0.01521062452762188</v>
+      </c>
+      <c r="Z4">
         <v>0.1028546236085088</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.06704788386596955</v>
-      </c>
-      <c r="AC3">
-        <v>-0.06704788386596955</v>
-      </c>
-      <c r="AD3">
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06703990172917093</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06703990172917093</v>
+      </c>
+      <c r="AD4">
         <v>3117.8</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
         <v>3117.8</v>
       </c>
-      <c r="AG3">
+      <c r="AG4">
         <v>2508.5</v>
       </c>
-      <c r="AH3">
+      <c r="AH4">
         <v>0.6456810321618655</v>
       </c>
-      <c r="AI3">
+      <c r="AI4">
         <v>0.6531475856289934</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ4">
         <v>0.5945158079347775</v>
       </c>
-      <c r="AK3">
+      <c r="AK4">
         <v>0.6023966187983286</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>0</v>
       </c>
     </row>
